--- a/artfynd/A 37138-2021 artfynd.xlsx
+++ b/artfynd/A 37138-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37138-2021 artfynd.xlsx
+++ b/artfynd/A 37138-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>949620</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446280.8807214833</v>
+        <v>446281</v>
       </c>
       <c r="R2" t="n">
-        <v>6531738.650879961</v>
+        <v>6531739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>1410998</v>
       </c>
       <c r="B3" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446334.2678623679</v>
+        <v>446334</v>
       </c>
       <c r="R3" t="n">
-        <v>6531560.257185516</v>
+        <v>6531560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +859,9 @@
           <t>2011-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
